--- a/busbuddy.xlsx
+++ b/busbuddy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\philip.otieno\Desktop\busbuddy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A20C11-E319-4448-B589-08F77A9FCCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F29B518-4872-4009-8252-6C3D015EF0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="10420" xr2:uid="{9F0F0F97-8A47-403A-8032-9D31B8DBB886}"/>
+    <workbookView xWindow="20" yWindow="620" windowWidth="19180" windowHeight="10180" xr2:uid="{9F0F0F97-8A47-403A-8032-9D31B8DBB886}"/>
   </bookViews>
   <sheets>
     <sheet name="Revenue" sheetId="1" r:id="rId1"/>
@@ -37,12 +37,6 @@
     <t>Metric</t>
   </si>
   <si>
-    <t>Target ($)</t>
-  </si>
-  <si>
-    <t>Achieved ($)</t>
-  </si>
-  <si>
     <t>% of Target</t>
   </si>
   <si>
@@ -83,6 +77,12 @@
   </si>
   <si>
     <t>Net Adds</t>
+  </si>
+  <si>
+    <t>Target (KES)</t>
+  </si>
+  <si>
+    <t>Achieved (KES)</t>
   </si>
 </sst>
 </file>
@@ -441,8 +441,8 @@
   <cols>
     <col min="1" max="1" width="26.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.6328125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -457,24 +457,24 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
         <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
       </c>
       <c r="D2" s="1">
         <v>1000000</v>
@@ -483,18 +483,19 @@
         <v>238000</v>
       </c>
       <c r="F2" s="2">
+        <f>E2/D2</f>
         <v>0.23799999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
         <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
       </c>
       <c r="D3" s="1">
         <v>1000000</v>
@@ -503,18 +504,19 @@
         <v>238000</v>
       </c>
       <c r="F3" s="2">
+        <f t="shared" ref="F3:F21" si="0">E3/D3</f>
         <v>0.23799999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
       </c>
       <c r="D4" s="1">
         <v>5000000</v>
@@ -523,18 +525,19 @@
         <v>1200000</v>
       </c>
       <c r="F4" s="2">
+        <f t="shared" si="0"/>
         <v>0.24</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" s="1">
         <v>1250000</v>
@@ -543,18 +546,19 @@
         <v>300000</v>
       </c>
       <c r="F5" s="2">
+        <f t="shared" si="0"/>
         <v>0.24</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D6" s="1">
         <v>1000000</v>
@@ -563,18 +567,19 @@
         <v>42000</v>
       </c>
       <c r="F6" s="2">
+        <f t="shared" si="0"/>
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
         <v>7</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
       </c>
       <c r="D7" s="1">
         <v>1000000</v>
@@ -583,18 +588,19 @@
         <v>35700</v>
       </c>
       <c r="F7" s="2">
+        <f t="shared" si="0"/>
         <v>3.5700000000000003E-2</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D8" s="1">
         <v>5000000</v>
@@ -603,18 +609,19 @@
         <v>19300</v>
       </c>
       <c r="F8" s="2">
-        <v>3.8999999999999998E-3</v>
+        <f t="shared" si="0"/>
+        <v>3.8600000000000001E-3</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D9" s="1">
         <v>1250000</v>
@@ -623,18 +630,19 @@
         <v>15440</v>
       </c>
       <c r="F9" s="2">
-        <v>1.24E-2</v>
+        <f t="shared" si="0"/>
+        <v>1.2352E-2</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D10" s="1">
         <v>1000000</v>
@@ -643,18 +651,19 @@
         <v>36200</v>
       </c>
       <c r="F10" s="2">
+        <f t="shared" si="0"/>
         <v>3.6200000000000003E-2</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
         <v>7</v>
-      </c>
-      <c r="C11" t="s">
-        <v>9</v>
       </c>
       <c r="D11" s="1">
         <v>1000000</v>
@@ -663,18 +672,19 @@
         <v>30770</v>
       </c>
       <c r="F11" s="2">
-        <v>3.0800000000000001E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.0769999999999999E-2</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D12" s="1">
         <v>5000000</v>
@@ -683,18 +693,19 @@
         <v>27800</v>
       </c>
       <c r="F12" s="2">
-        <v>5.5999999999999999E-3</v>
+        <f t="shared" si="0"/>
+        <v>5.5599999999999998E-3</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D13" s="1">
         <v>1250000</v>
@@ -703,18 +714,19 @@
         <v>22400</v>
       </c>
       <c r="F13" s="2">
-        <v>1.7899999999999999E-2</v>
+        <f t="shared" si="0"/>
+        <v>1.7919999999999998E-2</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D14" s="1">
         <v>1000000</v>
@@ -723,18 +735,19 @@
         <v>36200</v>
       </c>
       <c r="F14" s="2">
+        <f t="shared" si="0"/>
         <v>3.6200000000000003E-2</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" t="s">
         <v>7</v>
-      </c>
-      <c r="C15" t="s">
-        <v>9</v>
       </c>
       <c r="D15" s="1">
         <v>1000000</v>
@@ -743,18 +756,19 @@
         <v>30770</v>
       </c>
       <c r="F15" s="2">
-        <v>3.0800000000000001E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.0769999999999999E-2</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D16" s="1">
         <v>5000000</v>
@@ -763,18 +777,19 @@
         <v>27800</v>
       </c>
       <c r="F16" s="2">
-        <v>5.5999999999999999E-3</v>
+        <f t="shared" si="0"/>
+        <v>5.5599999999999998E-3</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D17" s="1">
         <v>1250000</v>
@@ -783,87 +798,100 @@
         <v>22400</v>
       </c>
       <c r="F17" s="2">
-        <v>1.7899999999999999E-2</v>
+        <f t="shared" si="0"/>
+        <v>1.7919999999999998E-2</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D18" s="1">
+        <f>SUM(D2,D6,D10,D14)</f>
         <v>4000000</v>
       </c>
       <c r="E18" s="1">
+        <f>SUM(E2,E6,E10,E14)</f>
         <v>352400</v>
       </c>
       <c r="F18" s="2">
+        <f t="shared" si="0"/>
         <v>8.8099999999999998E-2</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" t="s">
         <v>7</v>
       </c>
-      <c r="C19" t="s">
-        <v>9</v>
-      </c>
       <c r="D19" s="1">
+        <f>SUM(D3,D7,D11,D15)</f>
         <v>4000000</v>
       </c>
       <c r="E19" s="1">
+        <f>SUM(E3,E7,E11,E15)</f>
         <v>335240</v>
       </c>
       <c r="F19" s="2">
-        <v>8.3799999999999999E-2</v>
+        <f t="shared" si="0"/>
+        <v>8.3809999999999996E-2</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D20" s="1">
+        <f>SUM(D4,D8,D12,D16)</f>
         <v>20000000</v>
       </c>
       <c r="E20" s="1">
+        <f>SUM(E4,E8,E12,E16)</f>
         <v>1274900</v>
       </c>
       <c r="F20" s="2">
-        <v>6.3700000000000007E-2</v>
+        <f t="shared" si="0"/>
+        <v>6.3744999999999996E-2</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D21" s="1">
+        <f>SUM(D5,D9,D13,D17)</f>
         <v>5000000</v>
       </c>
       <c r="E21" s="1">
+        <f>SUM(E5,E9,E13,E17)</f>
         <v>360240</v>
       </c>
       <c r="F21" s="2">
-        <v>7.1999999999999995E-2</v>
+        <f t="shared" si="0"/>
+        <v>7.2048000000000001E-2</v>
       </c>
     </row>
   </sheetData>
@@ -879,7 +907,8 @@
     <col min="1" max="1" width="26.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.08984375" customWidth="1"/>
+    <col min="5" max="5" width="11.08984375" customWidth="1"/>
     <col min="6" max="6" width="15.54296875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -894,24 +923,24 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>300</v>
@@ -920,18 +949,19 @@
         <v>22</v>
       </c>
       <c r="F2" s="2">
-        <v>0.88</v>
+        <f>E2/D2</f>
+        <v>7.3333333333333334E-2</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3">
         <v>12</v>
@@ -940,18 +970,19 @@
         <v>20</v>
       </c>
       <c r="F3" s="2">
-        <v>0.90900000000000003</v>
+        <f t="shared" ref="F3:F21" si="0">E3/D3</f>
+        <v>1.6666666666666667</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>300</v>
@@ -960,18 +991,19 @@
         <v>15</v>
       </c>
       <c r="F4" s="2">
-        <v>0.83299999999999996</v>
+        <f t="shared" si="0"/>
+        <v>0.05</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>12</v>
@@ -980,18 +1012,19 @@
         <v>12</v>
       </c>
       <c r="F5" s="2">
-        <v>0.8</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>300</v>
@@ -1000,18 +1033,19 @@
         <v>26</v>
       </c>
       <c r="F6" s="2">
-        <v>1.04</v>
+        <f t="shared" si="0"/>
+        <v>8.666666666666667E-2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D7">
         <v>12</v>
@@ -1020,18 +1054,19 @@
         <v>22</v>
       </c>
       <c r="F7" s="2">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>1.8333333333333333</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D8">
         <v>300</v>
@@ -1040,18 +1075,19 @@
         <v>15</v>
       </c>
       <c r="F8" s="2">
-        <v>0.83299999999999996</v>
+        <f t="shared" si="0"/>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D9">
         <v>12</v>
@@ -1060,18 +1096,19 @@
         <v>11</v>
       </c>
       <c r="F9" s="2">
-        <v>0.73299999999999998</v>
+        <f t="shared" si="0"/>
+        <v>0.91666666666666663</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D10">
         <v>300</v>
@@ -1080,18 +1117,19 @@
         <v>24</v>
       </c>
       <c r="F10" s="2">
-        <v>0.8</v>
+        <f t="shared" si="0"/>
+        <v>0.08</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D11">
         <v>12</v>
@@ -1100,18 +1138,19 @@
         <v>20</v>
       </c>
       <c r="F11" s="2">
-        <v>0.8</v>
+        <f t="shared" si="0"/>
+        <v>1.6666666666666667</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>300</v>
@@ -1120,18 +1159,19 @@
         <v>15</v>
       </c>
       <c r="F12" s="2">
-        <v>0.75</v>
+        <f t="shared" si="0"/>
+        <v>0.05</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1140,18 +1180,19 @@
         <v>10</v>
       </c>
       <c r="F13" s="2">
-        <v>0.66700000000000004</v>
+        <f t="shared" si="0"/>
+        <v>0.83333333333333337</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D14">
         <v>300</v>
@@ -1160,18 +1201,19 @@
         <v>24</v>
       </c>
       <c r="F14" s="2">
-        <v>0.8</v>
+        <f t="shared" si="0"/>
+        <v>0.08</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D15">
         <v>12</v>
@@ -1180,18 +1222,19 @@
         <v>20</v>
       </c>
       <c r="F15" s="2">
-        <v>0.8</v>
+        <f t="shared" si="0"/>
+        <v>1.6666666666666667</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D16">
         <v>300</v>
@@ -1200,18 +1243,19 @@
         <v>15</v>
       </c>
       <c r="F16" s="2">
-        <v>0.75</v>
+        <f t="shared" si="0"/>
+        <v>0.05</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D17">
         <v>12</v>
@@ -1220,87 +1264,100 @@
         <v>10</v>
       </c>
       <c r="F17" s="2">
-        <v>0.66700000000000004</v>
+        <f t="shared" si="0"/>
+        <v>0.83333333333333337</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D18">
+        <f>SUM(D2,D6,D10,D14)</f>
         <v>1200</v>
       </c>
       <c r="E18">
+        <f>SUM(E2,E6,E10,E14)</f>
         <v>96</v>
       </c>
       <c r="F18" s="2">
-        <v>0.66700000000000004</v>
+        <f>E18/D18</f>
+        <v>0.08</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D19">
+        <f>SUM(D3,D7,D11,D15)</f>
         <v>48</v>
       </c>
       <c r="E19">
+        <f>SUM(E3,E7,E11,E15)</f>
         <v>82</v>
       </c>
       <c r="F19" s="2">
-        <v>0.66700000000000004</v>
+        <f>E19/D19</f>
+        <v>1.7083333333333333</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D20">
+        <f>SUM(D4,D8,D12,D16)</f>
         <v>1200</v>
       </c>
       <c r="E20">
+        <f>SUM(E4,E8,E12,E16)</f>
         <v>60</v>
       </c>
       <c r="F20" s="2">
-        <v>0.66700000000000004</v>
+        <f t="shared" si="0"/>
+        <v>0.05</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D21">
+        <f>SUM(D5,D9,D13,D17)</f>
         <v>48</v>
       </c>
       <c r="E21">
+        <f>SUM(E5,E9,E13,E17)</f>
         <v>43</v>
       </c>
       <c r="F21" s="2">
-        <v>0.66700000000000004</v>
+        <f t="shared" si="0"/>
+        <v>0.89583333333333337</v>
       </c>
     </row>
   </sheetData>

--- a/busbuddy.xlsx
+++ b/busbuddy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\philip.otieno\Desktop\busbuddy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F29B518-4872-4009-8252-6C3D015EF0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F33795D-A38A-46D8-AAFF-83CADE3AABA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="620" windowWidth="19180" windowHeight="10180" xr2:uid="{9F0F0F97-8A47-403A-8032-9D31B8DBB886}"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="10420" xr2:uid="{9F0F0F97-8A47-403A-8032-9D31B8DBB886}"/>
   </bookViews>
   <sheets>
     <sheet name="Revenue" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="22">
   <si>
     <t>Quarter</t>
   </si>
@@ -84,13 +84,30 @@
   <si>
     <t>Achieved (KES)</t>
   </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Peter</t>
+  </si>
+  <si>
+    <t>Mercy</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -118,10 +135,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -436,462 +454,771 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBA22660-3BC3-4A4B-A6B4-A8489B19DE97}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.90625" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" customWidth="1"/>
+    <col min="4" max="4" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="13.6328125" customWidth="1"/>
+    <col min="7" max="7" width="15.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1">
-        <v>1000000</v>
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="E2" s="1">
-        <v>238000</v>
-      </c>
-      <c r="F2" s="2">
-        <f>E2/D2</f>
-        <v>0.23799999999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>2000000</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G2" s="2">
+        <f>F2/E2</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="1">
-        <v>1000000</v>
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="E3" s="1">
-        <v>238000</v>
-      </c>
-      <c r="F3" s="2">
-        <f t="shared" ref="F3:F21" si="0">E3/D3</f>
-        <v>0.23799999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <v>5000000</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G3" s="2">
+        <f t="shared" ref="G3:G31" si="0">F3/E3</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="1">
-        <v>5000000</v>
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="E4" s="1">
-        <v>1200000</v>
-      </c>
-      <c r="F4" s="2">
-        <f t="shared" si="0"/>
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+        <v>1250000</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G4" s="2">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="1">
-        <v>1250000</v>
-      </c>
       <c r="E5" s="1">
-        <v>300000</v>
-      </c>
-      <c r="F5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+        <v>1000000</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G5" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="1">
-        <v>1000000</v>
-      </c>
       <c r="E6" s="1">
-        <v>42000</v>
-      </c>
-      <c r="F6" s="2">
-        <f t="shared" si="0"/>
-        <v>4.2000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+        <v>5000000</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G6" s="2">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="1">
-        <v>1000000</v>
-      </c>
       <c r="E7" s="1">
-        <v>35700</v>
-      </c>
-      <c r="F7" s="2">
-        <f t="shared" si="0"/>
-        <v>3.5700000000000003E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+        <v>1250000</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G7" s="2">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G8" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="1">
+      <c r="E9" s="1">
         <v>5000000</v>
       </c>
-      <c r="E8" s="1">
-        <v>19300</v>
-      </c>
-      <c r="F8" s="2">
-        <f t="shared" si="0"/>
-        <v>3.8600000000000001E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="1">
-        <v>1250000</v>
-      </c>
-      <c r="E9" s="1">
-        <v>15440</v>
-      </c>
-      <c r="F9" s="2">
-        <f t="shared" si="0"/>
-        <v>1.2352E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F9" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G9" s="2">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1250000</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G10" s="2">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G11" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="E10" s="1">
-        <v>36200</v>
-      </c>
-      <c r="F10" s="2">
-        <f t="shared" si="0"/>
-        <v>3.6200000000000003E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="E12" s="1">
+        <v>5000000</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G12" s="2">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1250000</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G13" s="2">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="1">
+        <f>SUM(E2,E5,E8,E11)</f>
+        <v>5000000</v>
+      </c>
+      <c r="F14" s="1">
+        <f>SUM(F2,F5,F8,F11)</f>
+        <v>4000000</v>
+      </c>
+      <c r="G14" s="2">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="1">
+        <f>SUM(E3,E6,E9,E12)</f>
+        <v>20000000</v>
+      </c>
+      <c r="F15" s="1">
+        <f>SUM(F3,F6,F9,F12)</f>
+        <v>4000000</v>
+      </c>
+      <c r="G15" s="2">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="1">
+        <f>SUM(E4,E7,E10,E13)</f>
+        <v>5000000</v>
+      </c>
+      <c r="F16" s="1">
+        <f>SUM(F4,F7,F10,F13)</f>
+        <v>4000000</v>
+      </c>
+      <c r="G16" s="2">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2000000</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G17" s="2">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="1">
+        <v>5000000</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G18" s="2">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1250000</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G19" s="2">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G20" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="1">
+        <v>5000000</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G21" s="2">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1250000</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G22" s="2">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="E11" s="1">
-        <v>30770</v>
-      </c>
-      <c r="F11" s="2">
-        <f t="shared" si="0"/>
-        <v>3.0769999999999999E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="E23" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G23" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>10</v>
       </c>
-      <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="1">
+      <c r="E24" s="1">
         <v>5000000</v>
       </c>
-      <c r="E12" s="1">
-        <v>27800</v>
-      </c>
-      <c r="F12" s="2">
-        <f t="shared" si="0"/>
-        <v>5.5599999999999998E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="F24" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G24" s="2">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>10</v>
       </c>
-      <c r="B13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="1">
+      <c r="E25" s="1">
         <v>1250000</v>
       </c>
-      <c r="E13" s="1">
-        <v>22400</v>
-      </c>
-      <c r="F13" s="2">
-        <f t="shared" si="0"/>
-        <v>1.7919999999999998E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="F25" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G25" s="2">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>11</v>
       </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G26" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="E14" s="1">
-        <v>36200</v>
-      </c>
-      <c r="F14" s="2">
-        <f t="shared" si="0"/>
-        <v>3.6200000000000003E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="E27" s="1">
+        <v>5000000</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G27" s="2">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>11</v>
       </c>
-      <c r="B15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B28" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="E15" s="1">
-        <v>30770</v>
-      </c>
-      <c r="F15" s="2">
-        <f t="shared" si="0"/>
-        <v>3.0769999999999999E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="E28" s="1">
+        <v>1250000</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G28" s="2">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="1">
+        <f>SUM(E17,E20,E23,E26)</f>
+        <v>5000000</v>
+      </c>
+      <c r="F29" s="1">
+        <f>SUM(F17,F20,F23,F26)</f>
+        <v>4000000</v>
+      </c>
+      <c r="G29" s="2">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="1">
+      <c r="E30" s="1">
+        <f>SUM(E18,E21,E24,E27)</f>
+        <v>20000000</v>
+      </c>
+      <c r="F30" s="1">
+        <f>SUM(F18,F21,F24,F27)</f>
+        <v>4000000</v>
+      </c>
+      <c r="G30" s="2">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="1">
+        <f>SUM(E19,E22,E25,E28)</f>
         <v>5000000</v>
       </c>
-      <c r="E16" s="1">
-        <v>27800</v>
-      </c>
-      <c r="F16" s="2">
-        <f t="shared" si="0"/>
-        <v>5.5599999999999998E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="1">
-        <v>1250000</v>
-      </c>
-      <c r="E17" s="1">
-        <v>22400</v>
-      </c>
-      <c r="F17" s="2">
-        <f t="shared" si="0"/>
-        <v>1.7919999999999998E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="1">
-        <f>SUM(D2,D6,D10,D14)</f>
+      <c r="F31" s="1">
+        <f>SUM(F19,F22,F25,F28)</f>
         <v>4000000</v>
       </c>
-      <c r="E18" s="1">
-        <f>SUM(E2,E6,E10,E14)</f>
-        <v>352400</v>
-      </c>
-      <c r="F18" s="2">
-        <f t="shared" si="0"/>
-        <v>8.8099999999999998E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="1">
-        <f>SUM(D3,D7,D11,D15)</f>
-        <v>4000000</v>
-      </c>
-      <c r="E19" s="1">
-        <f>SUM(E3,E7,E11,E15)</f>
-        <v>335240</v>
-      </c>
-      <c r="F19" s="2">
-        <f t="shared" si="0"/>
-        <v>8.3809999999999996E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="1">
-        <f>SUM(D4,D8,D12,D16)</f>
-        <v>20000000</v>
-      </c>
-      <c r="E20" s="1">
-        <f>SUM(E4,E8,E12,E16)</f>
-        <v>1274900</v>
-      </c>
-      <c r="F20" s="2">
-        <f t="shared" si="0"/>
-        <v>6.3744999999999996E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="1">
-        <f>SUM(D5,D9,D13,D17)</f>
-        <v>5000000</v>
-      </c>
-      <c r="E21" s="1">
-        <f>SUM(E5,E9,E13,E17)</f>
-        <v>360240</v>
-      </c>
-      <c r="F21" s="2">
-        <f t="shared" si="0"/>
-        <v>7.2048000000000001E-2</v>
+      <c r="G31" s="2">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -901,461 +1228,1013 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{948BC0A7-A618-40D4-B678-C01E96D87ECF}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.08984375" customWidth="1"/>
+    <col min="2" max="2" width="13.6328125" customWidth="1"/>
+    <col min="3" max="3" width="11.54296875" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" customWidth="1"/>
     <col min="5" max="5" width="11.08984375" customWidth="1"/>
-    <col min="6" max="6" width="15.54296875" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" customWidth="1"/>
+    <col min="7" max="7" width="14.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2">
         <v>300</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>22</v>
       </c>
-      <c r="F2" s="2">
-        <f>E2/D2</f>
+      <c r="G2" s="2">
+        <f>F2/E2</f>
         <v>7.3333333333333334E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="D3">
-        <v>12</v>
-      </c>
       <c r="E3">
-        <v>20</v>
-      </c>
-      <c r="F3" s="2">
-        <f t="shared" ref="F3:F21" si="0">E3/D3</f>
+        <v>12</v>
+      </c>
+      <c r="F3">
+        <v>20</v>
+      </c>
+      <c r="G3" s="2">
+        <f t="shared" ref="G3:G41" si="0">F3/E3</f>
         <v>1.6666666666666667</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4">
         <v>300</v>
       </c>
-      <c r="E4">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2">
+      <c r="F4">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2">
         <f t="shared" si="0"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
         <v>16</v>
       </c>
-      <c r="D5">
-        <v>12</v>
-      </c>
       <c r="E5">
         <v>12</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6">
         <v>300</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>26</v>
       </c>
-      <c r="F6" s="2">
+      <c r="G6" s="2">
         <f t="shared" si="0"/>
         <v>8.666666666666667E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
         <v>16</v>
       </c>
-      <c r="D7">
-        <v>12</v>
-      </c>
       <c r="E7">
+        <v>12</v>
+      </c>
+      <c r="F7">
         <v>22</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <f t="shared" si="0"/>
         <v>1.8333333333333333</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8">
+        <v>8</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8">
         <v>300</v>
       </c>
-      <c r="E8">
-        <v>15</v>
-      </c>
-      <c r="F8" s="2">
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8" s="2">
         <f t="shared" si="0"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
         <v>16</v>
       </c>
-      <c r="D9">
-        <v>12</v>
-      </c>
       <c r="E9">
+        <v>12</v>
+      </c>
+      <c r="F9">
         <v>11</v>
       </c>
-      <c r="F9" s="2">
+      <c r="G9" s="2">
         <f t="shared" si="0"/>
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10">
         <v>300</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>24</v>
       </c>
-      <c r="F10" s="2">
+      <c r="G10" s="2">
         <f t="shared" si="0"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" t="s">
         <v>16</v>
       </c>
-      <c r="D11">
-        <v>12</v>
-      </c>
       <c r="E11">
-        <v>20</v>
-      </c>
-      <c r="F11" s="2">
+        <v>12</v>
+      </c>
+      <c r="F11">
+        <v>20</v>
+      </c>
+      <c r="G11" s="2">
         <f t="shared" si="0"/>
         <v>1.6666666666666667</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12">
         <v>300</v>
       </c>
-      <c r="E12">
-        <v>15</v>
-      </c>
-      <c r="F12" s="2">
+      <c r="F12">
+        <v>15</v>
+      </c>
+      <c r="G12" s="2">
         <f t="shared" si="0"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" t="s">
         <v>16</v>
       </c>
-      <c r="D13">
-        <v>12</v>
-      </c>
       <c r="E13">
+        <v>12</v>
+      </c>
+      <c r="F13">
         <v>10</v>
       </c>
-      <c r="F13" s="2">
+      <c r="G13" s="2">
         <f t="shared" si="0"/>
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14">
+        <v>5</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14">
         <v>300</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>24</v>
       </c>
-      <c r="F14" s="2">
+      <c r="G14" s="2">
         <f t="shared" si="0"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" t="s">
         <v>16</v>
       </c>
-      <c r="D15">
-        <v>12</v>
-      </c>
       <c r="E15">
-        <v>20</v>
-      </c>
-      <c r="F15" s="2">
+        <v>12</v>
+      </c>
+      <c r="F15">
+        <v>20</v>
+      </c>
+      <c r="G15" s="2">
         <f t="shared" si="0"/>
         <v>1.6666666666666667</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16">
+        <v>8</v>
+      </c>
+      <c r="D16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16">
         <v>300</v>
       </c>
-      <c r="E16">
-        <v>15</v>
-      </c>
-      <c r="F16" s="2">
+      <c r="F16">
+        <v>15</v>
+      </c>
+      <c r="G16" s="2">
         <f t="shared" si="0"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" t="s">
         <v>16</v>
       </c>
-      <c r="D17">
-        <v>12</v>
-      </c>
       <c r="E17">
+        <v>12</v>
+      </c>
+      <c r="F17">
         <v>10</v>
       </c>
-      <c r="F17" s="2">
+      <c r="G17" s="2">
         <f t="shared" si="0"/>
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18">
-        <f>SUM(D2,D6,D10,D14)</f>
-        <v>1200</v>
+        <v>5</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
       </c>
       <c r="E18">
         <f>SUM(E2,E6,E10,E14)</f>
+        <v>1200</v>
+      </c>
+      <c r="F18">
+        <f>SUM(F2,F6,F10,F14)</f>
         <v>96</v>
       </c>
-      <c r="F18" s="2">
-        <f>E18/D18</f>
+      <c r="G18" s="2">
+        <f t="shared" si="0"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" t="s">
         <v>16</v>
-      </c>
-      <c r="D19">
-        <f>SUM(D3,D7,D11,D15)</f>
-        <v>48</v>
       </c>
       <c r="E19">
         <f>SUM(E3,E7,E11,E15)</f>
+        <v>48</v>
+      </c>
+      <c r="F19">
+        <f>SUM(F3,F7,F11,F15)</f>
         <v>82</v>
       </c>
-      <c r="F19" s="2">
-        <f>E19/D19</f>
+      <c r="G19" s="2">
+        <f t="shared" si="0"/>
         <v>1.7083333333333333</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20">
-        <f>SUM(D4,D8,D12,D16)</f>
-        <v>1200</v>
+        <v>8</v>
+      </c>
+      <c r="D20" t="s">
+        <v>15</v>
       </c>
       <c r="E20">
         <f>SUM(E4,E8,E12,E16)</f>
+        <v>1200</v>
+      </c>
+      <c r="F20">
+        <f>SUM(F4,F8,F12,F16)</f>
         <v>60</v>
       </c>
-      <c r="F20" s="2">
+      <c r="G20" s="2">
         <f t="shared" si="0"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" t="s">
         <v>16</v>
-      </c>
-      <c r="D21">
-        <f>SUM(D5,D9,D13,D17)</f>
-        <v>48</v>
       </c>
       <c r="E21">
         <f>SUM(E5,E9,E13,E17)</f>
+        <v>48</v>
+      </c>
+      <c r="F21">
+        <f>SUM(F5,F9,F13,F17)</f>
         <v>43</v>
       </c>
-      <c r="F21" s="2">
+      <c r="G21" s="2">
+        <f t="shared" si="0"/>
+        <v>0.89583333333333337</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22">
+        <v>300</v>
+      </c>
+      <c r="F22">
+        <v>22</v>
+      </c>
+      <c r="G22" s="2">
+        <f t="shared" si="0"/>
+        <v>7.3333333333333334E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23">
+        <v>12</v>
+      </c>
+      <c r="F23">
+        <v>20</v>
+      </c>
+      <c r="G23" s="2">
+        <f t="shared" si="0"/>
+        <v>1.6666666666666667</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24">
+        <v>300</v>
+      </c>
+      <c r="F24">
+        <v>15</v>
+      </c>
+      <c r="G24" s="2">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25">
+        <v>12</v>
+      </c>
+      <c r="F25">
+        <v>12</v>
+      </c>
+      <c r="G25" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26">
+        <v>300</v>
+      </c>
+      <c r="F26">
+        <v>26</v>
+      </c>
+      <c r="G26" s="2">
+        <f t="shared" si="0"/>
+        <v>8.666666666666667E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27">
+        <v>12</v>
+      </c>
+      <c r="F27">
+        <v>22</v>
+      </c>
+      <c r="G27" s="2">
+        <f t="shared" si="0"/>
+        <v>1.8333333333333333</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28">
+        <v>300</v>
+      </c>
+      <c r="F28">
+        <v>15</v>
+      </c>
+      <c r="G28" s="2">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29">
+        <v>12</v>
+      </c>
+      <c r="F29">
+        <v>11</v>
+      </c>
+      <c r="G29" s="2">
+        <f t="shared" si="0"/>
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30">
+        <v>300</v>
+      </c>
+      <c r="F30">
+        <v>24</v>
+      </c>
+      <c r="G30" s="2">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31">
+        <v>12</v>
+      </c>
+      <c r="F31">
+        <v>20</v>
+      </c>
+      <c r="G31" s="2">
+        <f t="shared" si="0"/>
+        <v>1.6666666666666667</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32">
+        <v>300</v>
+      </c>
+      <c r="F32">
+        <v>15</v>
+      </c>
+      <c r="G32" s="2">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33">
+        <v>12</v>
+      </c>
+      <c r="F33">
+        <v>10</v>
+      </c>
+      <c r="G33" s="2">
+        <f t="shared" si="0"/>
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34">
+        <v>300</v>
+      </c>
+      <c r="F34">
+        <v>24</v>
+      </c>
+      <c r="G34" s="2">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" t="s">
+        <v>21</v>
+      </c>
+      <c r="C35" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35">
+        <v>12</v>
+      </c>
+      <c r="F35">
+        <v>20</v>
+      </c>
+      <c r="G35" s="2">
+        <f t="shared" si="0"/>
+        <v>1.6666666666666667</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36">
+        <v>300</v>
+      </c>
+      <c r="F36">
+        <v>15</v>
+      </c>
+      <c r="G36" s="2">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" t="s">
+        <v>21</v>
+      </c>
+      <c r="C37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37">
+        <v>12</v>
+      </c>
+      <c r="F37">
+        <v>10</v>
+      </c>
+      <c r="G37" s="2">
+        <f t="shared" si="0"/>
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38">
+        <f>SUM(E22,E26,E30,E34)</f>
+        <v>1200</v>
+      </c>
+      <c r="F38">
+        <f>SUM(F22,F26,F30,F34)</f>
+        <v>96</v>
+      </c>
+      <c r="G38" s="2">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39">
+        <f>SUM(E23,E27,E31,E35)</f>
+        <v>48</v>
+      </c>
+      <c r="F39">
+        <f>SUM(F23,F27,F31,F35)</f>
+        <v>82</v>
+      </c>
+      <c r="G39" s="2">
+        <f t="shared" si="0"/>
+        <v>1.7083333333333333</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40">
+        <f>SUM(E24,E28,E32,E36)</f>
+        <v>1200</v>
+      </c>
+      <c r="F40">
+        <f>SUM(F24,F28,F32,F36)</f>
+        <v>60</v>
+      </c>
+      <c r="G40" s="2">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41">
+        <f>SUM(E25,E29,E33,E37)</f>
+        <v>48</v>
+      </c>
+      <c r="F41">
+        <f>SUM(F25,F29,F33,F37)</f>
+        <v>43</v>
+      </c>
+      <c r="G41" s="2">
         <f t="shared" si="0"/>
         <v>0.89583333333333337</v>
       </c>

--- a/busbuddy.xlsx
+++ b/busbuddy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\philip.otieno\Desktop\busbuddy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F33795D-A38A-46D8-AAFF-83CADE3AABA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE992C7-C29F-41BD-ADE6-C7466CD7839C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="10420" xr2:uid="{9F0F0F97-8A47-403A-8032-9D31B8DBB886}"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{9F0F0F97-8A47-403A-8032-9D31B8DBB886}"/>
   </bookViews>
   <sheets>
     <sheet name="Revenue" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="23">
   <si>
     <t>Quarter</t>
   </si>
@@ -93,6 +93,9 @@
   <si>
     <t>Mercy</t>
   </si>
+  <si>
+    <t>Free Trial</t>
+  </si>
 </sst>
 </file>
 
@@ -115,12 +118,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -135,11 +144,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -778,79 +790,79 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="A14" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="1" t="s">
+      <c r="B14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="1">
-        <f>SUM(E2,E5,E8,E11)</f>
+      <c r="E14" s="6">
+        <f t="shared" ref="E14:F16" si="1">SUM(E2,E5,E8,E11)</f>
         <v>5000000</v>
       </c>
-      <c r="F14" s="1">
-        <f>SUM(F2,F5,F8,F11)</f>
+      <c r="F14" s="6">
+        <f t="shared" si="1"/>
         <v>4000000</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="5">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="A15" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="1" t="s">
+      <c r="B15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E15" s="1">
-        <f>SUM(E3,E6,E9,E12)</f>
+      <c r="E15" s="6">
+        <f t="shared" si="1"/>
         <v>20000000</v>
       </c>
-      <c r="F15" s="1">
-        <f>SUM(F3,F6,F9,F12)</f>
+      <c r="F15" s="6">
+        <f t="shared" si="1"/>
         <v>4000000</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="5">
         <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="A16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="1" t="s">
+      <c r="B16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="1">
-        <f>SUM(E4,E7,E10,E13)</f>
+      <c r="E16" s="6">
+        <f t="shared" si="1"/>
         <v>5000000</v>
       </c>
-      <c r="F16" s="1">
-        <f>SUM(F4,F7,F10,F13)</f>
+      <c r="F16" s="6">
+        <f t="shared" si="1"/>
         <v>4000000</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="5">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
@@ -1144,79 +1156,79 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+      <c r="A29" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B29" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="B29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="1">
-        <f>SUM(E17,E20,E23,E26)</f>
+      <c r="E29" s="6">
+        <f t="shared" ref="E29:F31" si="2">SUM(E17,E20,E23,E26)</f>
         <v>5000000</v>
       </c>
-      <c r="F29" s="1">
-        <f>SUM(F17,F20,F23,F26)</f>
+      <c r="F29" s="6">
+        <f t="shared" si="2"/>
         <v>4000000</v>
       </c>
-      <c r="G29" s="2">
+      <c r="G29" s="5">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+      <c r="A30" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B30" t="s">
-        <v>21</v>
-      </c>
-      <c r="C30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="B30" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E30" s="1">
-        <f>SUM(E18,E21,E24,E27)</f>
+      <c r="E30" s="6">
+        <f t="shared" si="2"/>
         <v>20000000</v>
       </c>
-      <c r="F30" s="1">
-        <f>SUM(F18,F21,F24,F27)</f>
+      <c r="F30" s="6">
+        <f t="shared" si="2"/>
         <v>4000000</v>
       </c>
-      <c r="G30" s="2">
+      <c r="G30" s="5">
         <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+      <c r="A31" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B31" t="s">
-        <v>21</v>
-      </c>
-      <c r="C31" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="B31" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="1">
-        <f>SUM(E19,E22,E25,E28)</f>
+      <c r="E31" s="6">
+        <f t="shared" si="2"/>
         <v>5000000</v>
       </c>
-      <c r="F31" s="1">
-        <f>SUM(F19,F22,F25,F28)</f>
+      <c r="F31" s="6">
+        <f t="shared" si="2"/>
         <v>4000000</v>
       </c>
-      <c r="G31" s="2">
+      <c r="G31" s="5">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
@@ -1228,7 +1240,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{948BC0A7-A618-40D4-B678-C01E96D87ECF}">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.7265625" bestFit="1" customWidth="1"/>
@@ -1277,14 +1289,14 @@
         <v>15</v>
       </c>
       <c r="E2">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2">
-        <f>F2/E2</f>
-        <v>7.3333333333333334E-2</v>
+        <f>IFERROR((F2/E2),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -1301,14 +1313,14 @@
         <v>16</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" ref="G3:G41" si="0">F3/E3</f>
-        <v>1.6666666666666667</v>
+        <f t="shared" ref="G3:G51" si="0">IFERROR((F3/E3),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -1319,20 +1331,20 @@
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -1346,41 +1358,41 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2">
         <f t="shared" si="0"/>
-        <v>8.666666666666667E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -1394,17 +1406,17 @@
         <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="F7">
-        <v>22</v>
+        <v>145</v>
       </c>
       <c r="G7" s="2">
         <f t="shared" si="0"/>
-        <v>1.8333333333333333</v>
+        <v>0.96666666666666667</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -1415,20 +1427,20 @@
         <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8">
         <v>15</v>
       </c>
-      <c r="E8">
-        <v>300</v>
-      </c>
       <c r="F8">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -1439,68 +1451,68 @@
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2">
         <f t="shared" si="0"/>
-        <v>0.91666666666666663</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D10" t="s">
         <v>15</v>
       </c>
       <c r="E10">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D11" t="s">
         <v>16</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2">
         <f t="shared" si="0"/>
-        <v>1.6666666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -1511,7 +1523,7 @@
         <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D12" t="s">
         <v>15</v>
@@ -1520,11 +1532,11 @@
         <v>300</v>
       </c>
       <c r="F12">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -1535,7 +1547,7 @@
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D13" t="s">
         <v>16</v>
@@ -1544,16 +1556,16 @@
         <v>12</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2">
         <f t="shared" si="0"/>
-        <v>0.83333333333333337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
         <v>20</v>
@@ -1562,46 +1574,46 @@
         <v>5</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" t="s">
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E15">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2">
         <f t="shared" si="0"/>
-        <v>1.6666666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16" t="s">
         <v>20</v>
@@ -1610,17 +1622,17 @@
         <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E16">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G16" s="2">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -1631,51 +1643,49 @@
         <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E17">
-        <v>12</v>
+        <v>300</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G17" s="2">
         <f t="shared" si="0"/>
-        <v>0.83333333333333337</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18">
         <v>12</v>
       </c>
-      <c r="B18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18">
-        <f>SUM(E2,E6,E10,E14)</f>
-        <v>1200</v>
-      </c>
       <c r="F18">
-        <f>SUM(F2,F6,F10,F14)</f>
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="G18" s="2">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>1.6666666666666667</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
         <v>20</v>
@@ -1684,24 +1694,22 @@
         <v>5</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E19">
-        <f>SUM(E3,E7,E11,E15)</f>
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <f>SUM(F3,F7,F11,F15)</f>
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2">
         <f t="shared" si="0"/>
-        <v>1.7083333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
         <v>20</v>
@@ -1713,12 +1721,10 @@
         <v>15</v>
       </c>
       <c r="E20">
-        <f>SUM(E4,E8,E12,E16)</f>
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="F20">
-        <f>SUM(F4,F8,F12,F16)</f>
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="G20" s="2">
         <f t="shared" si="0"/>
@@ -1727,7 +1733,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
         <v>20</v>
@@ -1739,141 +1745,149 @@
         <v>16</v>
       </c>
       <c r="E21">
-        <f>SUM(E5,E9,E13,E17)</f>
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="F21">
-        <f>SUM(F5,F9,F13,F17)</f>
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="G21" s="2">
         <f t="shared" si="0"/>
-        <v>0.89583333333333337</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="A22" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="4">
+        <f>SUM(E2,E7,E12,E17)</f>
+        <v>750</v>
+      </c>
+      <c r="F22" s="4">
+        <f>SUM(F2,F7,F12,F17)</f>
+        <v>169</v>
+      </c>
+      <c r="G22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.22533333333333333</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="4">
+        <f t="shared" ref="E23:F23" si="1">SUM(E3,E8,E13,E18)</f>
+        <v>39</v>
+      </c>
+      <c r="F23" s="4">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="G23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.51282051282051277</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="4">
+        <f t="shared" ref="E24:F24" si="2">SUM(E4,E9,E14,E19)</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="4">
+        <f t="shared" ref="E25:F25" si="3">SUM(E5,E10,E15,E20)</f>
         <v>300</v>
       </c>
-      <c r="F22">
-        <v>22</v>
-      </c>
-      <c r="G22" s="2">
-        <f t="shared" si="0"/>
-        <v>7.3333333333333334E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="F25" s="4">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="G25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E23">
+      <c r="E26" s="4">
+        <f t="shared" ref="E26:F26" si="4">SUM(E6,E11,E16,E21)</f>
         <v>12</v>
       </c>
-      <c r="F23">
-        <v>20</v>
-      </c>
-      <c r="G23" s="2">
-        <f t="shared" si="0"/>
-        <v>1.6666666666666667</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24">
-        <v>300</v>
-      </c>
-      <c r="F24">
-        <v>15</v>
-      </c>
-      <c r="G24" s="2">
-        <f t="shared" si="0"/>
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E25">
-        <v>12</v>
-      </c>
-      <c r="F25">
-        <v>12</v>
-      </c>
-      <c r="G25" s="2">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26">
-        <v>300</v>
-      </c>
-      <c r="F26">
-        <v>26</v>
-      </c>
-      <c r="G26" s="2">
-        <f t="shared" si="0"/>
-        <v>8.666666666666667E-2</v>
+      <c r="F26" s="4">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="G26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.83333333333333337</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B27" t="s">
         <v>21</v>
@@ -1882,166 +1896,166 @@
         <v>5</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E27">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G27" s="2">
         <f t="shared" si="0"/>
-        <v>1.8333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B28" t="s">
         <v>21</v>
       </c>
       <c r="C28" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E28">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G28" s="2">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B29" t="s">
         <v>21</v>
       </c>
       <c r="C29" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E29">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G29" s="2">
         <f t="shared" si="0"/>
-        <v>0.91666666666666663</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B30" t="s">
         <v>21</v>
       </c>
       <c r="C30" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D30" t="s">
         <v>15</v>
       </c>
       <c r="E30">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G30" s="2">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B31" t="s">
         <v>21</v>
       </c>
       <c r="C31" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D31" t="s">
         <v>16</v>
       </c>
       <c r="E31">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G31" s="2">
         <f t="shared" si="0"/>
-        <v>1.6666666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B32" t="s">
         <v>21</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D32" t="s">
         <v>15</v>
       </c>
       <c r="E32">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="F32">
-        <v>15</v>
+        <v>186</v>
       </c>
       <c r="G32" s="2">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B33" t="s">
         <v>21</v>
       </c>
       <c r="C33" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D33" t="s">
         <v>16</v>
       </c>
       <c r="E33">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F33">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G33" s="2">
         <f t="shared" si="0"/>
-        <v>0.83333333333333337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B34" t="s">
         <v>21</v>
@@ -2050,46 +2064,46 @@
         <v>5</v>
       </c>
       <c r="D34" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E34">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G34" s="2">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B35" t="s">
         <v>21</v>
       </c>
       <c r="C35" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E35">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G35" s="2">
         <f t="shared" si="0"/>
-        <v>1.6666666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B36" t="s">
         <v>21</v>
@@ -2098,46 +2112,46 @@
         <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E36">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G36" s="2">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B37" t="s">
         <v>21</v>
       </c>
       <c r="C37" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E37">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G37" s="2">
         <f t="shared" si="0"/>
-        <v>0.83333333333333337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B38" t="s">
         <v>21</v>
@@ -2146,24 +2160,22 @@
         <v>5</v>
       </c>
       <c r="D38" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E38">
-        <f>SUM(E22,E26,E30,E34)</f>
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <f>SUM(F22,F26,F30,F34)</f>
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="G38" s="2">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B39" t="s">
         <v>21</v>
@@ -2172,24 +2184,22 @@
         <v>5</v>
       </c>
       <c r="D39" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E39">
-        <f>SUM(E23,E27,E31,E35)</f>
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <f>SUM(F23,F27,F31,F35)</f>
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="G39" s="2">
         <f t="shared" si="0"/>
-        <v>1.7083333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B40" t="s">
         <v>21</v>
@@ -2201,21 +2211,19 @@
         <v>15</v>
       </c>
       <c r="E40">
-        <f>SUM(E24,E28,E32,E36)</f>
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <f>SUM(F24,F28,F32,F36)</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G40" s="2">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B41" t="s">
         <v>21</v>
@@ -2227,16 +2235,264 @@
         <v>16</v>
       </c>
       <c r="E41">
-        <f>SUM(E25,E29,E33,E37)</f>
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <f>SUM(F25,F29,F33,F37)</f>
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="G41" s="2">
         <f t="shared" si="0"/>
-        <v>0.89583333333333337</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C42" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42">
+        <v>300</v>
+      </c>
+      <c r="F42">
+        <v>24</v>
+      </c>
+      <c r="G42" s="2">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43" t="s">
+        <v>21</v>
+      </c>
+      <c r="C43" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43">
+        <v>12</v>
+      </c>
+      <c r="F43">
+        <v>20</v>
+      </c>
+      <c r="G43" s="2">
+        <f t="shared" si="0"/>
+        <v>1.6666666666666667</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44" t="s">
+        <v>22</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45">
+        <v>300</v>
+      </c>
+      <c r="F45">
+        <v>15</v>
+      </c>
+      <c r="G45" s="2">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46">
+        <v>12</v>
+      </c>
+      <c r="F46">
+        <v>10</v>
+      </c>
+      <c r="G46" s="2">
+        <f t="shared" si="0"/>
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47" s="4">
+        <f>SUM(E27,E32,E37,E42)</f>
+        <v>450</v>
+      </c>
+      <c r="F47" s="4">
+        <f>SUM(F27,F32,F37,F42)</f>
+        <v>210</v>
+      </c>
+      <c r="G47" s="5">
+        <f t="shared" si="0"/>
+        <v>0.46666666666666667</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="4">
+        <f t="shared" ref="E48:F48" si="5">SUM(E28,E33,E38,E43)</f>
+        <v>27</v>
+      </c>
+      <c r="F48" s="4">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="G48" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7407407407407407</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E49" s="4">
+        <f t="shared" ref="E49:F49" si="6">SUM(E29,E34,E39,E44)</f>
+        <v>0</v>
+      </c>
+      <c r="F49" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G49" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A50" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="4">
+        <f t="shared" ref="E50:F50" si="7">SUM(E30,E35,E40,E45)</f>
+        <v>300</v>
+      </c>
+      <c r="F50" s="4">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="G50" s="5">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51" s="4">
+        <f t="shared" ref="E51:F51" si="8">SUM(E31,E36,E41,E46)</f>
+        <v>12</v>
+      </c>
+      <c r="F51" s="4">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="G51" s="5">
+        <f t="shared" si="0"/>
+        <v>0.83333333333333337</v>
       </c>
     </row>
   </sheetData>

--- a/busbuddy.xlsx
+++ b/busbuddy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\philip.otieno\Desktop\busbuddy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE992C7-C29F-41BD-ADE6-C7466CD7839C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6432EF55-C807-4DDE-B282-9478775B3636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{9F0F0F97-8A47-403A-8032-9D31B8DBB886}"/>
   </bookViews>
@@ -515,14 +515,14 @@
         <v>7</v>
       </c>
       <c r="E2" s="1">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2">
-        <f>F2/E2</f>
-        <v>0.5</v>
+        <f>IFERROR((F2/E2),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -539,14 +539,14 @@
         <v>6</v>
       </c>
       <c r="E3" s="1">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" ref="G3:G31" si="0">F3/E3</f>
-        <v>0.2</v>
+        <f t="shared" ref="G3:G31" si="0">IFERROR((F3/E3),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -563,14 +563,14 @@
         <v>7</v>
       </c>
       <c r="E4" s="1">
-        <v>1250000</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -587,14 +587,14 @@
         <v>7</v>
       </c>
       <c r="E5" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -611,14 +611,14 @@
         <v>6</v>
       </c>
       <c r="E6" s="1">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -635,14 +635,14 @@
         <v>7</v>
       </c>
       <c r="E7" s="1">
-        <v>1250000</v>
+        <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -659,14 +659,14 @@
         <v>7</v>
       </c>
       <c r="E8" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -683,14 +683,14 @@
         <v>6</v>
       </c>
       <c r="E9" s="1">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -707,14 +707,14 @@
         <v>7</v>
       </c>
       <c r="E10" s="1">
-        <v>1250000</v>
+        <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -731,14 +731,14 @@
         <v>7</v>
       </c>
       <c r="E11" s="1">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="F11" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -755,14 +755,14 @@
         <v>6</v>
       </c>
       <c r="E12" s="1">
-        <v>5000000</v>
+        <v>2500000</v>
       </c>
       <c r="F12" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -779,14 +779,14 @@
         <v>7</v>
       </c>
       <c r="E13" s="1">
-        <v>1250000</v>
+        <v>625000</v>
       </c>
       <c r="F13" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -804,15 +804,15 @@
       </c>
       <c r="E14" s="6">
         <f t="shared" ref="E14:F16" si="1">SUM(E2,E5,E8,E11)</f>
-        <v>5000000</v>
+        <v>500000</v>
       </c>
       <c r="F14" s="6">
         <f t="shared" si="1"/>
-        <v>4000000</v>
-      </c>
-      <c r="G14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -830,15 +830,15 @@
       </c>
       <c r="E15" s="6">
         <f t="shared" si="1"/>
-        <v>20000000</v>
+        <v>2500000</v>
       </c>
       <c r="F15" s="6">
         <f t="shared" si="1"/>
-        <v>4000000</v>
-      </c>
-      <c r="G15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
@@ -856,15 +856,15 @@
       </c>
       <c r="E16" s="6">
         <f t="shared" si="1"/>
-        <v>5000000</v>
+        <v>625000</v>
       </c>
       <c r="F16" s="6">
         <f t="shared" si="1"/>
-        <v>4000000</v>
-      </c>
-      <c r="G16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -881,14 +881,14 @@
         <v>7</v>
       </c>
       <c r="E17" s="1">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="F17" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -905,14 +905,14 @@
         <v>6</v>
       </c>
       <c r="E18" s="1">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="F18" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -929,14 +929,14 @@
         <v>7</v>
       </c>
       <c r="E19" s="1">
-        <v>1250000</v>
+        <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -953,14 +953,14 @@
         <v>7</v>
       </c>
       <c r="E20" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="F20" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -977,14 +977,14 @@
         <v>6</v>
       </c>
       <c r="E21" s="1">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -1001,14 +1001,14 @@
         <v>7</v>
       </c>
       <c r="E22" s="1">
-        <v>1250000</v>
+        <v>0</v>
       </c>
       <c r="F22" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -1025,14 +1025,14 @@
         <v>7</v>
       </c>
       <c r="E23" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="F23" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
@@ -1049,14 +1049,14 @@
         <v>6</v>
       </c>
       <c r="E24" s="1">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="F24" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -1073,14 +1073,14 @@
         <v>7</v>
       </c>
       <c r="E25" s="1">
-        <v>1250000</v>
+        <v>0</v>
       </c>
       <c r="F25" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
@@ -1097,14 +1097,14 @@
         <v>7</v>
       </c>
       <c r="E26" s="1">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="F26" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
@@ -1121,14 +1121,14 @@
         <v>6</v>
       </c>
       <c r="E27" s="1">
-        <v>5000000</v>
+        <v>2500000</v>
       </c>
       <c r="F27" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G27" s="2">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
@@ -1145,14 +1145,14 @@
         <v>7</v>
       </c>
       <c r="E28" s="1">
-        <v>1250000</v>
+        <v>625000</v>
       </c>
       <c r="F28" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G28" s="2">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
@@ -1170,15 +1170,15 @@
       </c>
       <c r="E29" s="6">
         <f t="shared" ref="E29:F31" si="2">SUM(E17,E20,E23,E26)</f>
-        <v>5000000</v>
+        <v>500000</v>
       </c>
       <c r="F29" s="6">
         <f t="shared" si="2"/>
-        <v>4000000</v>
-      </c>
-      <c r="G29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
+      </c>
+      <c r="G29" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
@@ -1196,15 +1196,15 @@
       </c>
       <c r="E30" s="6">
         <f t="shared" si="2"/>
-        <v>20000000</v>
+        <v>2500000</v>
       </c>
       <c r="F30" s="6">
         <f t="shared" si="2"/>
-        <v>4000000</v>
-      </c>
-      <c r="G30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="G30" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
@@ -1222,15 +1222,15 @@
       </c>
       <c r="E31" s="6">
         <f t="shared" si="2"/>
-        <v>5000000</v>
+        <v>625000</v>
       </c>
       <c r="F31" s="6">
         <f t="shared" si="2"/>
-        <v>4000000</v>
-      </c>
-      <c r="G31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
+      </c>
+      <c r="G31" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1577,14 +1577,14 @@
         <v>22</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -1697,14 +1697,14 @@
         <v>22</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G19" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -1822,15 +1822,15 @@
       </c>
       <c r="E24" s="4">
         <f t="shared" ref="E24:F24" si="2">SUM(E4,E9,E14,E19)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F24" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">

--- a/busbuddy.xlsx
+++ b/busbuddy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\philip.otieno\Desktop\busbuddy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6432EF55-C807-4DDE-B282-9478775B3636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71AC8A75-EEE2-435C-B751-A2D8804D7E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{9F0F0F97-8A47-403A-8032-9D31B8DBB886}"/>
   </bookViews>
@@ -734,11 +734,11 @@
         <v>500000</v>
       </c>
       <c r="F11" s="1">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="G11" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -758,11 +758,11 @@
         <v>2500000</v>
       </c>
       <c r="F12" s="1">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="G12" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -782,11 +782,11 @@
         <v>625000</v>
       </c>
       <c r="F13" s="1">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="G13" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -808,11 +808,11 @@
       </c>
       <c r="F14" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="G14" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -834,11 +834,11 @@
       </c>
       <c r="F15" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="G15" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
@@ -860,11 +860,11 @@
       </c>
       <c r="F16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="G16" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -1409,14 +1409,14 @@
         <v>15</v>
       </c>
       <c r="E7">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2">
         <f t="shared" si="0"/>
-        <v>0.96666666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -1433,7 +1433,7 @@
         <v>16</v>
       </c>
       <c r="E8">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1529,14 +1529,14 @@
         <v>15</v>
       </c>
       <c r="E12">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="G12" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.96666666666666667</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -1553,7 +1553,7 @@
         <v>16</v>
       </c>
       <c r="E13">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1577,14 +1577,14 @@
         <v>22</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="2">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -1649,14 +1649,14 @@
         <v>15</v>
       </c>
       <c r="E17">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="F17">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -1697,14 +1697,14 @@
         <v>22</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -1770,15 +1770,15 @@
       </c>
       <c r="E22" s="4">
         <f>SUM(E2,E7,E12,E17)</f>
-        <v>750</v>
+        <v>300</v>
       </c>
       <c r="F22" s="4">
         <f>SUM(F2,F7,F12,F17)</f>
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="0"/>
-        <v>0.22533333333333333</v>
+        <v>0.48333333333333334</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="E23" s="4">
         <f t="shared" ref="E23:F23" si="1">SUM(E3,E8,E13,E18)</f>
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F23" s="4">
         <f t="shared" si="1"/>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="G23" s="5">
         <f t="shared" si="0"/>
-        <v>0.51282051282051277</v>
+        <v>0.7407407407407407</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
@@ -1826,11 +1826,11 @@
       </c>
       <c r="F24" s="4">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -2187,14 +2187,14 @@
         <v>22</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G39" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
@@ -2307,7 +2307,7 @@
         <v>22</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -2432,15 +2432,15 @@
       </c>
       <c r="E49" s="4">
         <f t="shared" ref="E49:F49" si="6">SUM(E29,E34,E39,E44)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F49" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G49" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">

--- a/busbuddy.xlsx
+++ b/busbuddy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\philip.otieno\Desktop\busbuddy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71AC8A75-EEE2-435C-B751-A2D8804D7E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3B0792-4FE6-4A3B-9ECF-828695F30622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{9F0F0F97-8A47-403A-8032-9D31B8DBB886}"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="10420" xr2:uid="{9F0F0F97-8A47-403A-8032-9D31B8DBB886}"/>
   </bookViews>
   <sheets>
     <sheet name="Revenue" sheetId="1" r:id="rId1"/>
@@ -659,14 +659,14 @@
         <v>7</v>
       </c>
       <c r="E8" s="1">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="F8" s="1">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="G8" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -683,14 +683,14 @@
         <v>6</v>
       </c>
       <c r="E9" s="1">
-        <v>0</v>
+        <v>2500000</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="G9" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -707,14 +707,14 @@
         <v>7</v>
       </c>
       <c r="E10" s="1">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="F10" s="1">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="G10" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -734,11 +734,11 @@
         <v>500000</v>
       </c>
       <c r="F11" s="1">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -758,11 +758,11 @@
         <v>2500000</v>
       </c>
       <c r="F12" s="1">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -782,11 +782,11 @@
         <v>625000</v>
       </c>
       <c r="F13" s="1">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2">
         <f t="shared" si="0"/>
-        <v>0.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -804,7 +804,7 @@
       </c>
       <c r="E14" s="6">
         <f t="shared" ref="E14:F16" si="1">SUM(E2,E5,E8,E11)</f>
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="F14" s="6">
         <f t="shared" si="1"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="G14" s="2">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -830,15 +830,15 @@
       </c>
       <c r="E15" s="6">
         <f t="shared" si="1"/>
-        <v>2500000</v>
+        <v>5000000</v>
       </c>
       <c r="F15" s="6">
         <f t="shared" si="1"/>
-        <v>1000000</v>
+        <v>800000</v>
       </c>
       <c r="G15" s="2">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
@@ -856,15 +856,15 @@
       </c>
       <c r="E16" s="6">
         <f t="shared" si="1"/>
-        <v>625000</v>
+        <v>1625000</v>
       </c>
       <c r="F16" s="6">
         <f t="shared" si="1"/>
-        <v>300000</v>
+        <v>400000</v>
       </c>
       <c r="G16" s="2">
         <f t="shared" si="0"/>
-        <v>0.48</v>
+        <v>0.24615384615384617</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -1025,14 +1025,14 @@
         <v>7</v>
       </c>
       <c r="E23" s="1">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="F23" s="1">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="G23" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
@@ -1049,14 +1049,14 @@
         <v>6</v>
       </c>
       <c r="E24" s="1">
-        <v>0</v>
+        <v>2500000</v>
       </c>
       <c r="F24" s="1">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="G24" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -1073,14 +1073,14 @@
         <v>7</v>
       </c>
       <c r="E25" s="1">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="F25" s="1">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="G25" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
@@ -1170,15 +1170,15 @@
       </c>
       <c r="E29" s="6">
         <f t="shared" ref="E29:F31" si="2">SUM(E17,E20,E23,E26)</f>
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="F29" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="G29" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
@@ -1196,15 +1196,15 @@
       </c>
       <c r="E30" s="6">
         <f t="shared" si="2"/>
-        <v>2500000</v>
+        <v>5000000</v>
       </c>
       <c r="F30" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="G30" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
@@ -1222,15 +1222,15 @@
       </c>
       <c r="E31" s="6">
         <f t="shared" si="2"/>
-        <v>625000</v>
+        <v>1625000</v>
       </c>
       <c r="F31" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="G31" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.36923076923076925</v>
       </c>
     </row>
   </sheetData>
@@ -1676,11 +1676,11 @@
         <v>12</v>
       </c>
       <c r="F18">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2">
         <f t="shared" si="0"/>
-        <v>1.6666666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -1724,11 +1724,11 @@
         <v>300</v>
       </c>
       <c r="F20">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -1748,11 +1748,11 @@
         <v>12</v>
       </c>
       <c r="F21">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2">
         <f t="shared" si="0"/>
-        <v>0.83333333333333337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -1800,11 +1800,11 @@
       </c>
       <c r="F23" s="4">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="0"/>
-        <v>0.7407407407407407</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
@@ -1852,11 +1852,11 @@
       </c>
       <c r="F25" s="4">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
@@ -1878,11 +1878,11 @@
       </c>
       <c r="F26" s="4">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G26" s="5">
         <f t="shared" si="0"/>
-        <v>0.83333333333333337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
@@ -2046,11 +2046,11 @@
         <v>15</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6.6666666666666666E-2</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
@@ -2262,11 +2262,11 @@
         <v>300</v>
       </c>
       <c r="F42">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G42" s="2">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
@@ -2286,11 +2286,11 @@
         <v>12</v>
       </c>
       <c r="F43">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G43" s="2">
         <f t="shared" si="0"/>
-        <v>1.6666666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
@@ -2334,11 +2334,11 @@
         <v>300</v>
       </c>
       <c r="F45">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G45" s="2">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
@@ -2358,11 +2358,11 @@
         <v>12</v>
       </c>
       <c r="F46">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G46" s="2">
         <f t="shared" si="0"/>
-        <v>0.83333333333333337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
@@ -2384,11 +2384,11 @@
       </c>
       <c r="F47" s="4">
         <f>SUM(F27,F32,F37,F42)</f>
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="G47" s="5">
         <f t="shared" si="0"/>
-        <v>0.46666666666666667</v>
+        <v>0.41333333333333333</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
@@ -2410,11 +2410,11 @@
       </c>
       <c r="F48" s="4">
         <f t="shared" si="5"/>
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G48" s="5">
         <f t="shared" si="0"/>
-        <v>0.7407407407407407</v>
+        <v>3.7037037037037035E-2</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
@@ -2462,11 +2462,11 @@
       </c>
       <c r="F50" s="4">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G50" s="5">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
@@ -2488,11 +2488,11 @@
       </c>
       <c r="F51" s="4">
         <f t="shared" si="8"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G51" s="5">
         <f t="shared" si="0"/>
-        <v>0.83333333333333337</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
